--- a/schools-presentations/A Gymnasiou/kahoot/A5.3 Μ2 - Κίνδυνοι στο Διαδίκτυο.xlsx
+++ b/schools-presentations/A Gymnasiou/kahoot/A5.3 Μ2 - Κίνδυνοι στο Διαδίκτυο.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R099655c46db84d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R138f303a7106445e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF4CC"/>
+        <x:fgColor rgb="FFFFF1C7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -340,30 +340,30 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Question - max 95 characters</x:v>
+        <x:v>Question - max 120 characters</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Answer 1 - max 60 characters</x:v>
+        <x:v>Answer 1 - max 75 characters</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Answer 2 - max 60 characters</x:v>
+        <x:v>Answer 2 - max 75 characters</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Answer 3 - max 60 characters</x:v>
+        <x:v>Answer 3 - max 75 characters</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Answer 4 - max 60 characters</x:v>
+        <x:v>Answer 4 - max 75 characters</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
         <x:v>Time limit (sec)</x:v>
@@ -372,21 +372,21 @@
         <x:v>Correct answer(s)</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="58" customHeight="1">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>Ποιο θεωρείται ακατάλληλο περιεχόμενο;</x:v>
+        <x:v>Ποιο περιεχόμενο θεωρείται ακατάλληλο για ανήλικους;</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Υλικό που προάγει βία, ρατσισμό ή επιβλαβείς πράξεις</x:v>
+        <x:v>Υλικό βίας, ρατσισμού ή επικίνδυνων πράξεων</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Μια σχολική εκπαιδευτική σελίδα</x:v>
+        <x:v>Σελίδα σχολικής βιβλιοθήκης με βιβλιοκριτικές</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Ένα νόμιμο πρόγραμμα ζωγραφικής</x:v>
+        <x:v>Ιστοσελίδα εκμάθησης πληκτρολόγησης</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Ένα αρχείο με τις εργασίες μας</x:v>
+        <x:v>Βίντεο με οδηγίες χρήσης εφαρμογής γραφείου</x:v>
       </x:c>
       <x:c r="F2" s="14" t="n">
         <x:v>30</x:v>
@@ -395,182 +395,182 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="58" customHeight="1">
+    <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>Τι κάνουμε όταν συναντήσουμε ακατάλληλο περιεχόμενο;</x:v>
+        <x:v>Τι κάνουμε όταν συναντήσουμε σοβαρά ακατάλληλο περιεχόμενο;</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Το προωθούμε σε φίλους</x:v>
+        <x:v>Το αποθηκεύουμε ως απόδειξη στη συσκευή</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Το αναφέρουμε σε ενήλικα και το καταγγέλλουμε</x:v>
+        <x:v>Το μοιραζόμαστε μόνο με φίλους που εμπιστευόμαστε</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Το αποθηκεύουμε για αργότερα</x:v>
+        <x:v>Απαντούμε στον δημιουργό του περιεχομένου</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Απαντούμε στον άγνωστο αποστολέα</x:v>
+        <x:v>Κλείνουμε τη σελίδα και ενημερώνουμε έμπιστο ενήλικα</x:v>
       </x:c>
       <x:c r="F3" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>Τι δείχνουν οι αριθμοί 3, 7, 12, 16 και 18 του PEGI;</x:v>
+        <x:v>Τι δείχνουν οι αριθμοί ηλικίας του PEGI;</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
+        <x:v>Την απαιτούμενη ταχύτητα σύνδεσης</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
         <x:v>Την ηλικιακή καταλληλότητα του παιχνιδιού</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>Τη δυσκολία του παιχνιδιού</x:v>
-      </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Την τιμή αγοράς του παιχνιδιού</x:v>
+        <x:v>Τον αριθμό των επιτρεπόμενων παικτών</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Τον αριθμό των παικτών</x:v>
+        <x:v>Τη μέση διάρκεια ολοκλήρωσης</x:v>
       </x:c>
       <x:c r="F4" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>Τι σημαίνει η ένδειξη PEGI OK;</x:v>
+        <x:v>Τι δηλώνει η ένδειξη PEGI OK;</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
+        <x:v>Το παιχνίδι δεν περιέχει αγορές</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Το παιχνίδι λειτουργεί χωρίς Internet</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
         <x:v>Το online παιχνίδι είναι κατάλληλο για όλες τις ηλικίες</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="str">
-        <x:v>Το παιχνίδι απαιτεί σύνδεση με τράπεζα</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>Το παιχνίδι είναι μόνο για ενήλικες</x:v>
-      </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Το παιχνίδι δεν λειτουργεί στο Διαδίκτυο</x:v>
+        <x:v>Το παιχνίδι έχει ελεγχθεί από το σχολείο</x:v>
       </x:c>
       <x:c r="F5" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>Τι είναι η παραπληροφόρηση;</x:v>
+        <x:v>Τι είναι παραπληροφόρηση;</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Ψευδείς, τροποποιημένες ή ελλιπείς πληροφορίες</x:v>
+        <x:v>Η διαφορετική άποψη που τεκμηριώνεται με πηγές</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Μόνο μια παλιά φωτογραφία</x:v>
+        <x:v>Ψευδής, αλλοιωμένη ή ελλιπής πληροφορία</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Η νόμιμη αγορά ενός βιβλίου</x:v>
+        <x:v>Μια παλιά είδηση που αναφέρει σωστά την ημερομηνία</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Η χρήση antivirus</x:v>
+        <x:v>Μια περίληψη που παραπέμπει στο αρχικό άρθρο</x:v>
       </x:c>
       <x:c r="F6" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>Πώς ελέγχουμε αν μια πληροφορία είναι αξιόπιστη;</x:v>
+        <x:v>Πώς ελέγχουμε καλύτερα την αξιοπιστία μιας διαδικτυακής πληροφορίας;</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Τη δεχόμαστε αν έχει ωραία εικόνα</x:v>
+        <x:v>Μετράμε πόσες εικόνες έχει η σελίδα</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Ελέγχουμε συγγραφέα και τη διασταυρώνουμε</x:v>
+        <x:v>Ελέγχουμε μόνο αν βρίσκεται πρώτη στα αποτελέσματα</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Τη δεχόμαστε αν τη μοιράστηκαν πολλοί</x:v>
+        <x:v>Ελέγχουμε συγγραφέα, ημερομηνία και ανεξάρτητες πηγές</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Ελέγχουμε μόνο το χρώμα της ιστοσελίδας</x:v>
+        <x:v>Τη δεχόμαστε αν έχει κοινοποιηθεί πολλές φορές</x:v>
       </x:c>
       <x:c r="F7" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>Ποιο είναι παράδειγμα παραβίασης πνευματικών δικαιωμάτων;</x:v>
+        <x:v>Ποιο αποτελεί παραβίαση πνευματικών δικαιωμάτων;</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Νόμιμη αγορά μουσικής</x:v>
+        <x:v>Αντιγραφή και διανομή έργου χωρίς άδεια</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Αντιγραφή μουσικής χωρίς άδεια του δημιουργού</x:v>
+        <x:v>Αγορά ενός νόμιμου ψηφιακού αντιγράφου</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Ανάγνωση βιβλίου από βιβλιοθήκη</x:v>
+        <x:v>Χρήση δικού μας κειμένου σε εργασία</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Δημιουργία δικού μας προγράμματος</x:v>
+        <x:v>Αναφορά της πηγής σε ένα σύντομο απόσπασμα</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>Ποιο μπορεί να είναι σημάδι εθισμού στο Διαδίκτυο;</x:v>
+        <x:v>Ποιο μπορεί να είναι ένδειξη εθισμού στο Διαδίκτυο;</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Παραμέληση μαθημάτων, φίλων και ύπνου</x:v>
+        <x:v>Χρήση υπολογιστή για προγραμματισμένη σχολική εργασία</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Χρήση υπολογιστή για μία σχολική εργασία</x:v>
+        <x:v>Διάλειμμα μετά από μία ώρα παιχνιδιού</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Διάλειμμα μετά από λίγη ώρα</x:v>
+        <x:v>Συμμετοχή σε δραστηριότητες χωρίς οθόνη</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Συμμετοχή σε αθλητικές δραστηριότητες</x:v>
+        <x:v>Παραμέληση ύπνου, μαθημάτων και σχέσεων</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>Παιδί χρησιμοποιεί μόνο του το Διαδίκτυο 6 ώρες καθημερινά. Ποια λύση είναι πληρέστερη;</x:v>
+        <x:v>Μαθητής χρησιμοποιεί μόνος το Internet 6 ώρες καθημερινά. Ποια παρέμβαση είναι πληρέστερη;</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Περισσότερες ώρες για να συνηθίσει</x:v>
+        <x:v>Απότομη απαγόρευση χωρίς συζήτηση ή εναλλακτικές</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Όρια χρόνου, κοινόχρηστος χώρος και δραστηριότητες</x:v>
+        <x:v>Σαφή όρια, κοινόχρηστος χώρος, συζήτηση και άλλες δραστηριότητες</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>Αγνόηση μέχρι να εμφανιστεί σοβαρό πρόβλημα</x:v>
+        <x:v>Αγνόηση του θέματος μέχρι να πέσουν οι βαθμοί</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>Μόνο αγορά νέου υπολογιστή</x:v>
+        <x:v>Αγορά ταχύτερου υπολογιστή ώστε να τελειώνει νωρίτερα</x:v>
       </x:c>
       <x:c r="F10" s="15" t="n">
         <x:v>60</x:v>
@@ -579,21 +579,21 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+    <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="13" t="str">
-        <x:v>Σελίδα αντιγράφει τραγούδι χωρίς άδεια και γράφει ψευδή στοιχεία. Ποιοι κίνδυνοι υπάρχουν;</x:v>
+        <x:v>Σελίδα διανέμει τραγούδι χωρίς άδεια και χρησιμοποιεί ψευδή στοιχεία. Ποιοι κίνδυνοι συνδυάζονται;</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Spam και phishing</x:v>
+        <x:v>Μόνο ακατάλληλο περιεχόμενο και εθισμός</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Ιός και ακατάλληλο περιεχόμενο</x:v>
+        <x:v>Μόνο κακόβουλο λογισμικό και Spam</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
         <x:v>Πνευματικά δικαιώματα και παραπληροφόρηση</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Μόνο εθισμός</x:v>
+        <x:v>PEGI και αποκάλυψη κωδικού πρόσβασης</x:v>
       </x:c>
       <x:c r="F11" s="15" t="n">
         <x:v>60</x:v>
